--- a/YoungHoyos_JuanAndres_Taller2.xlsx
+++ b/YoungHoyos_JuanAndres_Taller2.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,15 +172,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Aptos"/>
+        <b val="1"/>
+        <color rgb="001D5FBF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EAF0FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2205,7 +2222,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Politicas'!K4</f>
+              <f>'Politicas'!P4</f>
             </strRef>
           </tx>
           <spPr>
@@ -2232,12 +2249,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Politicas'!$J$5:$J$13</f>
+              <f>'Politicas'!$M$5:$M$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Politicas'!$K$5:$K$13</f>
+              <f>'Politicas'!$P$5:$P$13</f>
             </numRef>
           </val>
         </ser>
@@ -2246,7 +2263,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Politicas'!L4</f>
+              <f>'Politicas'!Q4</f>
             </strRef>
           </tx>
           <spPr>
@@ -2273,12 +2290,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Politicas'!$J$5:$J$13</f>
+              <f>'Politicas'!$M$5:$M$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Politicas'!$L$5:$L$13</f>
+              <f>'Politicas'!$Q$5:$Q$13</f>
             </numRef>
           </val>
         </ser>
@@ -2647,12 +2664,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6120000" cy="3420000"/>
+    <ext cx="6480000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -56457,20 +56474,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -56483,7 +56510,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>100 réplicas por combinación y caso de demanda (Paso A9): se cambian s y Q en Parametros, se recalcula y se guardan los estadísticos como valores.</t>
+          <t>Paso A9: se cambian s y Q en Parametros, se recalculan las 100 réplicas y los cuatro estadísticos se guardan como valores (columnas D:G). Lo demás son fórmulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>Criterio de selección (calculado con fórmulas)</t>
         </is>
       </c>
     </row>
@@ -56523,24 +56557,74 @@
           <t>Ventas perdidas por día</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Error estándar de la media</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Servicio completo</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Diferencia vs. recomendada</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Política</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Uniforme</t>
+          <t>s</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Empírica</t>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia uniforme</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia empírica</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Promedio de ambos</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>Servicio completo</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Desv. estándar promedio</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>Brecha vs. mejor con servicio</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Empate estadístico (&lt; 2 EE)</t>
         </is>
       </c>
     </row>
@@ -56568,17 +56652,61 @@
       <c r="G5" s="27" t="n">
         <v>0.08201277955271566</v>
       </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>s=5, Q=10</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n">
+      <c r="H5" s="9">
+        <f>E5/SQRT(100)</f>
+        <v>264589.31429960544</v>
+      </c>
+      <c r="I5" s="5" t="str">
+        <f>IF(F5=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J5" s="9">
+        <f>D5-SUMIFS($D$5:$D$22,$A$5:$A$22,A5,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-1046702.799999997</v>
+      </c>
+      <c r="K5" s="35" t="str">
+        <f>IF(AND(B5=PuntoReorden,C5=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M5" s="5" t="str">
+        <f>"s="&amp;N5&amp;", Q="&amp;O5</f>
+        <v>s=5, Q=10</v>
+      </c>
+      <c r="N5" s="12">
+        <f>B5</f>
+        <v>5</v>
+      </c>
+      <c r="O5" s="12">
+        <f>C5</f>
+        <v>10</v>
+      </c>
+      <c r="P5" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N5,$C$5:$C$22,O5)</f>
         <v>101939216</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="Q5" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N5,$C$5:$C$22,O5)</f>
         <v>102317104</v>
+      </c>
+      <c r="R5" s="36">
+        <f>AVERAGE(P5:Q5)</f>
+        <v>102128160</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N5,$C$5:$C$22,O5,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="T5" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N5,$C$5:$C$22,O5)</f>
+        <v>2618191.865441544</v>
+      </c>
+      <c r="U5" s="9" t="str">
+        <f>IF(S5="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R5,"–")</f>
+        <v>–</v>
+      </c>
+      <c r="V5" s="5" t="str">
+        <f>IF(S5="Sí",IF(U5&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>–</v>
       </c>
     </row>
     <row r="6">
@@ -56605,17 +56733,61 @@
       <c r="G6" s="27" t="n">
         <v>0.05549520766773162</v>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>s=5, Q=15</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="n">
+      <c r="H6" s="9">
+        <f>E6/SQRT(100)</f>
+        <v>324795.4168360427</v>
+      </c>
+      <c r="I6" s="5" t="str">
+        <f>IF(F6=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J6" s="9">
+        <f>D6-SUMIFS($D$5:$D$22,$A$5:$A$22,A6,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>852754</v>
+      </c>
+      <c r="K6" s="35" t="str">
+        <f>IF(AND(B6=PuntoReorden,C6=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M6" s="5" t="str">
+        <f>"s="&amp;N6&amp;", Q="&amp;O6</f>
+        <v>s=5, Q=15</v>
+      </c>
+      <c r="N6" s="12">
+        <f>B6</f>
+        <v>5</v>
+      </c>
+      <c r="O6" s="12">
+        <f>C6</f>
+        <v>15</v>
+      </c>
+      <c r="P6" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N6,$C$5:$C$22,O6)</f>
         <v>103838672.8</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="Q6" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N6,$C$5:$C$22,O6)</f>
         <v>103825750</v>
+      </c>
+      <c r="R6" s="36">
+        <f>AVERAGE(P6:Q6)</f>
+        <v>103832211.4</v>
+      </c>
+      <c r="S6" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N6,$C$5:$C$22,O6,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="T6" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N6,$C$5:$C$22,O6)</f>
+        <v>3123902.5587123665</v>
+      </c>
+      <c r="U6" s="9" t="str">
+        <f>IF(S6="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R6,"–")</f>
+        <v>–</v>
+      </c>
+      <c r="V6" s="5" t="str">
+        <f>IF(S6="Sí",IF(U6&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>–</v>
       </c>
     </row>
     <row r="7">
@@ -56642,17 +56814,61 @@
       <c r="G7" s="27" t="n">
         <v>0.02047923322683706</v>
       </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>s=6, Q=10</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="n">
+      <c r="H7" s="9">
+        <f>E7/SQRT(100)</f>
+        <v>245047.24368621758</v>
+      </c>
+      <c r="I7" s="5" t="str">
+        <f>IF(F7=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J7" s="9">
+        <f>D7-SUMIFS($D$5:$D$22,$A$5:$A$22,A7,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-123525.20000000298</v>
+      </c>
+      <c r="K7" s="35" t="str">
+        <f>IF(AND(B7=PuntoReorden,C7=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M7" s="5" t="str">
+        <f>"s="&amp;N7&amp;", Q="&amp;O7</f>
+        <v>s=6, Q=10</v>
+      </c>
+      <c r="N7" s="12">
+        <f>B7</f>
+        <v>6</v>
+      </c>
+      <c r="O7" s="12">
+        <f>C7</f>
+        <v>10</v>
+      </c>
+      <c r="P7" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N7,$C$5:$C$22,O7)</f>
         <v>102862393.6</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="Q7" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N7,$C$5:$C$22,O7)</f>
         <v>102845517.2</v>
+      </c>
+      <c r="R7" s="36">
+        <f>AVERAGE(P7:Q7)</f>
+        <v>102853955.4</v>
+      </c>
+      <c r="S7" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N7,$C$5:$C$22,O7,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="T7" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N7,$C$5:$C$22,O7)</f>
+        <v>2419083.4090529014</v>
+      </c>
+      <c r="U7" s="9" t="str">
+        <f>IF(S7="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R7,"–")</f>
+        <v>–</v>
+      </c>
+      <c r="V7" s="5" t="str">
+        <f>IF(S7="Sí",IF(U7&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>–</v>
       </c>
     </row>
     <row r="8">
@@ -56679,17 +56895,61 @@
       <c r="G8" s="27" t="n">
         <v>0.01313099041533546</v>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>s=6, Q=15</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="n">
+      <c r="H8" s="9">
+        <f>E8/SQRT(100)</f>
+        <v>369246.5478209059</v>
+      </c>
+      <c r="I8" s="5" t="str">
+        <f>IF(F8=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J8" s="9">
+        <f>D8-SUMIFS($D$5:$D$22,$A$5:$A$22,A8,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>922769.200000003</v>
+      </c>
+      <c r="K8" s="35" t="str">
+        <f>IF(AND(B8=PuntoReorden,C8=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M8" s="5" t="str">
+        <f>"s="&amp;N8&amp;", Q="&amp;O8</f>
+        <v>s=6, Q=15</v>
+      </c>
+      <c r="N8" s="12">
+        <f>B8</f>
+        <v>6</v>
+      </c>
+      <c r="O8" s="12">
+        <f>C8</f>
+        <v>15</v>
+      </c>
+      <c r="P8" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N8,$C$5:$C$22,O8)</f>
         <v>103908688</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="Q8" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N8,$C$5:$C$22,O8)</f>
         <v>102990297.2</v>
+      </c>
+      <c r="R8" s="36">
+        <f>AVERAGE(P8:Q8)</f>
+        <v>103449492.6</v>
+      </c>
+      <c r="S8" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N8,$C$5:$C$22,O8,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="T8" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N8,$C$5:$C$22,O8)</f>
+        <v>3407414.978964626</v>
+      </c>
+      <c r="U8" s="9" t="str">
+        <f>IF(S8="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R8,"–")</f>
+        <v>–</v>
+      </c>
+      <c r="V8" s="5" t="str">
+        <f>IF(S8="Sí",IF(U8&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>–</v>
       </c>
     </row>
     <row r="9">
@@ -56716,58 +56976,142 @@
       <c r="G9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="7" t="n"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>s=7, Q=10</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="n">
+      <c r="H9" s="9">
+        <f>E9/SQRT(100)</f>
+        <v>285077.8452118408</v>
+      </c>
+      <c r="I9" s="5" t="str">
+        <f>IF(F9=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J9" s="9">
+        <f>D9-SUMIFS($D$5:$D$22,$A$5:$A$22,A9,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>156661.20000000298</v>
+      </c>
+      <c r="K9" s="35" t="str">
+        <f>IF(AND(B9=PuntoReorden,C9=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M9" s="5" t="str">
+        <f>"s="&amp;N9&amp;", Q="&amp;O9</f>
+        <v>s=7, Q=10</v>
+      </c>
+      <c r="N9" s="12">
+        <f>B9</f>
+        <v>7</v>
+      </c>
+      <c r="O9" s="12">
+        <f>C9</f>
+        <v>10</v>
+      </c>
+      <c r="P9" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N9,$C$5:$C$22,O9)</f>
         <v>103142580</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="Q9" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N9,$C$5:$C$22,O9)</f>
         <v>102845421.2</v>
       </c>
+      <c r="R9" s="36">
+        <f>AVERAGE(P9:Q9)</f>
+        <v>102994000.6</v>
+      </c>
+      <c r="S9" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N9,$C$5:$C$22,O9,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="T9" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N9,$C$5:$C$22,O9)</f>
+        <v>2509476.115381105</v>
+      </c>
+      <c r="U9" s="9">
+        <f>IF(S9="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R9,"–")</f>
+        <v>696718.6000000089</v>
+      </c>
+      <c r="V9" s="5" t="str">
+        <f>IF(S9="Sí",IF(U9&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>Sí</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Uniforme</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D10" s="36" t="n">
+      <c r="D10" s="9" t="n">
         <v>102985918.8</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="9" t="n">
         <v>3147847.676580956</v>
       </c>
-      <c r="F10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="39" t="inlineStr">
-        <is>
-          <t>Recomendada (cargada en Parametros)</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>s=7, Q=15</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="n">
+      <c r="F10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <f>E10/SQRT(100)</f>
+        <v>314784.76765809563</v>
+      </c>
+      <c r="I10" s="5" t="str">
+        <f>IF(F10=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J10" s="9">
+        <f>D10-SUMIFS($D$5:$D$22,$A$5:$A$22,A10,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="35" t="str">
+        <f>IF(AND(B10=PuntoReorden,C10=CantPedido),"Recomendada","")</f>
+        <v>Recomendada</v>
+      </c>
+      <c r="M10" s="5" t="str">
+        <f>"s="&amp;N10&amp;", Q="&amp;O10</f>
+        <v>s=7, Q=15</v>
+      </c>
+      <c r="N10" s="12">
+        <f>B10</f>
+        <v>7</v>
+      </c>
+      <c r="O10" s="12">
+        <f>C10</f>
+        <v>15</v>
+      </c>
+      <c r="P10" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N10,$C$5:$C$22,O10)</f>
         <v>102985918.8</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="Q10" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N10,$C$5:$C$22,O10)</f>
         <v>102872550.4</v>
+      </c>
+      <c r="R10" s="36">
+        <f>AVERAGE(P10:Q10)</f>
+        <v>102929234.6</v>
+      </c>
+      <c r="S10" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N10,$C$5:$C$22,O10,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="T10" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N10,$C$5:$C$22,O10)</f>
+        <v>3148159.533936919</v>
+      </c>
+      <c r="U10" s="9">
+        <f>IF(S10="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R10,"–")</f>
+        <v>761484.6000000089</v>
+      </c>
+      <c r="V10" s="5" t="str">
+        <f>IF(S10="Sí",IF(U10&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>Sí</v>
       </c>
     </row>
     <row r="11">
@@ -56794,17 +57138,61 @@
       <c r="G11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="7" t="n"/>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>s=7, Q=20</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="n">
+      <c r="H11" s="9">
+        <f>E11/SQRT(100)</f>
+        <v>436011.0734767708</v>
+      </c>
+      <c r="I11" s="5" t="str">
+        <f>IF(F11=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J11" s="9">
+        <f>D11-SUMIFS($D$5:$D$22,$A$5:$A$22,A11,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>1163183.600000009</v>
+      </c>
+      <c r="K11" s="35" t="str">
+        <f>IF(AND(B11=PuntoReorden,C11=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M11" s="5" t="str">
+        <f>"s="&amp;N11&amp;", Q="&amp;O11</f>
+        <v>s=7, Q=20</v>
+      </c>
+      <c r="N11" s="12">
+        <f>B11</f>
+        <v>7</v>
+      </c>
+      <c r="O11" s="12">
+        <f>C11</f>
+        <v>20</v>
+      </c>
+      <c r="P11" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N11,$C$5:$C$22,O11)</f>
         <v>104149102.4</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="Q11" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N11,$C$5:$C$22,O11)</f>
         <v>103232336</v>
+      </c>
+      <c r="R11" s="36">
+        <f>AVERAGE(P11:Q11)</f>
+        <v>103690719.2</v>
+      </c>
+      <c r="S11" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N11,$C$5:$C$22,O11,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="T11" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N11,$C$5:$C$22,O11)</f>
+        <v>4118034.583075427</v>
+      </c>
+      <c r="U11" s="9">
+        <f>IF(S11="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R11,"–")</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="str">
+        <f>IF(S11="Sí",IF(U11&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>Sí</v>
       </c>
     </row>
     <row r="12">
@@ -56831,17 +57219,61 @@
       <c r="G12" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="7" t="n"/>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>s=7, Q=30</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>99256794.40000001</v>
-      </c>
-      <c r="L12" s="9" t="n">
+      <c r="H12" s="9">
+        <f>E12/SQRT(100)</f>
+        <v>549794.3342572937</v>
+      </c>
+      <c r="I12" s="5" t="str">
+        <f>IF(F12=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J12" s="9">
+        <f>D12-SUMIFS($D$5:$D$22,$A$5:$A$22,A12,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-3729124.399999991</v>
+      </c>
+      <c r="K12" s="35" t="str">
+        <f>IF(AND(B12=PuntoReorden,C12=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M12" s="5" t="str">
+        <f>"s="&amp;N12&amp;", Q="&amp;O12</f>
+        <v>s=7, Q=30</v>
+      </c>
+      <c r="N12" s="12">
+        <f>B12</f>
+        <v>7</v>
+      </c>
+      <c r="O12" s="12">
+        <f>C12</f>
+        <v>30</v>
+      </c>
+      <c r="P12" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N12,$C$5:$C$22,O12)</f>
+        <v>99256794.4</v>
+      </c>
+      <c r="Q12" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N12,$C$5:$C$22,O12)</f>
         <v>101183327.6</v>
+      </c>
+      <c r="R12" s="36">
+        <f>AVERAGE(P12:Q12)</f>
+        <v>100220061</v>
+      </c>
+      <c r="S12" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N12,$C$5:$C$22,O12,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="T12" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N12,$C$5:$C$22,O12)</f>
+        <v>5508469.757282492</v>
+      </c>
+      <c r="U12" s="9">
+        <f>IF(S12="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R12,"–")</f>
+        <v>3470658.200000003</v>
+      </c>
+      <c r="V12" s="5" t="str">
+        <f>IF(S12="Sí",IF(U12&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>No</v>
       </c>
     </row>
     <row r="13">
@@ -56868,17 +57300,61 @@
       <c r="G13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="7" t="n"/>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>s=8, Q=15</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="n">
+      <c r="H13" s="9">
+        <f>E13/SQRT(100)</f>
+        <v>323025.9931245338</v>
+      </c>
+      <c r="I13" s="5" t="str">
+        <f>IF(F13=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J13" s="9">
+        <f>D13-SUMIFS($D$5:$D$22,$A$5:$A$22,A13,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-428972.39999999106</v>
+      </c>
+      <c r="K13" s="35" t="str">
+        <f>IF(AND(B13=PuntoReorden,C13=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M13" s="5" t="str">
+        <f>"s="&amp;N13&amp;", Q="&amp;O13</f>
+        <v>s=8, Q=15</v>
+      </c>
+      <c r="N13" s="12">
+        <f>B13</f>
+        <v>8</v>
+      </c>
+      <c r="O13" s="12">
+        <f>C13</f>
+        <v>15</v>
+      </c>
+      <c r="P13" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Uniforme",$B$5:$B$22,N13,$C$5:$C$22,O13)</f>
         <v>102556946.4</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="Q13" s="9">
+        <f>SUMIFS($D$5:$D$22,$A$5:$A$22,"Empírica",$B$5:$B$22,N13,$C$5:$C$22,O13)</f>
         <v>102602372.4</v>
+      </c>
+      <c r="R13" s="36">
+        <f>AVERAGE(P13:Q13)</f>
+        <v>102579659.4</v>
+      </c>
+      <c r="S13" s="5" t="str">
+        <f>IF(COUNTIFS($B$5:$B$22,N13,$C$5:$C$22,O13,$F$5:$F$22,"&gt;0")=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="T13" s="9">
+        <f>AVERAGEIFS($E$5:$E$22,$B$5:$B$22,N13,$C$5:$C$22,O13)</f>
+        <v>3247671.013916773</v>
+      </c>
+      <c r="U13" s="9">
+        <f>IF(S13="Sí",_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")-R13,"–")</f>
+        <v>1111059.799999997</v>
+      </c>
+      <c r="V13" s="5" t="str">
+        <f>IF(S13="Sí",IF(U13&lt;2*$R$18,"Sí","No"),"–")</f>
+        <v>No</v>
       </c>
     </row>
     <row r="14">
@@ -56905,7 +57381,22 @@
       <c r="G14" s="27" t="n">
         <v>0.05971246006389776</v>
       </c>
-      <c r="H14" s="7" t="n"/>
+      <c r="H14" s="9">
+        <f>E14/SQRT(100)</f>
+        <v>259049.05878870338</v>
+      </c>
+      <c r="I14" s="5" t="str">
+        <f>IF(F14=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J14" s="9">
+        <f>D14-SUMIFS($D$5:$D$22,$A$5:$A$22,A14,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-555446.400000006</v>
+      </c>
+      <c r="K14" s="35" t="str">
+        <f>IF(AND(B14=PuntoReorden,C14=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -56931,7 +57422,31 @@
       <c r="G15" s="27" t="n">
         <v>0.03757188498402556</v>
       </c>
-      <c r="H15" s="7" t="n"/>
+      <c r="H15" s="9">
+        <f>E15/SQRT(100)</f>
+        <v>299985.0949064306</v>
+      </c>
+      <c r="I15" s="5" t="str">
+        <f>IF(F15=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J15" s="9">
+        <f>D15-SUMIFS($D$5:$D$22,$A$5:$A$22,A15,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>953199.599999994</v>
+      </c>
+      <c r="K15" s="35" t="str">
+        <f>IF(AND(B15=PuntoReorden,C15=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Mejor promedio con servicio completo</t>
+        </is>
+      </c>
+      <c r="R15" s="37" t="str">
+        <f>INDEX($M$5:$M$13,MATCH(_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí"),$R$5:$R$13,0))</f>
+        <v>s=7, Q=20</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -56957,7 +57472,31 @@
       <c r="G16" s="27" t="n">
         <v>0.009680511182108626</v>
       </c>
-      <c r="H16" s="7" t="n"/>
+      <c r="H16" s="9">
+        <f>E16/SQRT(100)</f>
+        <v>238769.4381243627</v>
+      </c>
+      <c r="I16" s="5" t="str">
+        <f>IF(F16=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J16" s="9">
+        <f>D16-SUMIFS($D$5:$D$22,$A$5:$A$22,A16,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-27033.20000000298</v>
+      </c>
+      <c r="K16" s="35" t="str">
+        <f>IF(AND(B16=PuntoReorden,C16=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Ganancia promedio de esa política</t>
+        </is>
+      </c>
+      <c r="R16" s="38">
+        <f>_xlfn.MAXIFS($R$5:$R$13,$S$5:$S$13,"Sí")</f>
+        <v>103690719.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -56983,7 +57522,31 @@
       <c r="G17" s="27" t="n">
         <v>0.005591054313099041</v>
       </c>
-      <c r="H17" s="7" t="n"/>
+      <c r="H17" s="9">
+        <f>E17/SQRT(100)</f>
+        <v>312236.4479720193</v>
+      </c>
+      <c r="I17" s="5" t="str">
+        <f>IF(F17=0,"Sí","No")</f>
+        <v>No</v>
+      </c>
+      <c r="J17" s="9">
+        <f>D17-SUMIFS($D$5:$D$22,$A$5:$A$22,A17,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>117746.79999999702</v>
+      </c>
+      <c r="K17" s="35" t="str">
+        <f>IF(AND(B17=PuntoReorden,C17=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Política cargada en Parametros</t>
+        </is>
+      </c>
+      <c r="R17" s="37" t="str">
+        <f>"s="&amp;PuntoReorden&amp;", Q="&amp;CantPedido</f>
+        <v>s=7, Q=15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -57009,36 +57572,80 @@
       <c r="G18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="9">
+        <f>E18/SQRT(100)</f>
+        <v>216817.3778643802</v>
+      </c>
+      <c r="I18" s="5" t="str">
+        <f>IF(F18=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J18" s="9">
+        <f>D18-SUMIFS($D$5:$D$22,$A$5:$A$22,A18,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-27129.20000000298</v>
+      </c>
+      <c r="K18" s="35" t="str">
+        <f>IF(AND(B18=PuntoReorden,C18=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Error estándar de una diferencia (√2 · EE)</t>
+        </is>
+      </c>
+      <c r="R18" s="38">
+        <f>SQRT(2)*AVERAGEIFS($H$5:$H$22,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>445216.9909407753</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Empírica</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" s="6" t="n">
+      <c r="B19" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="9" t="n">
         <v>102872550.4</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="9" t="n">
         <v>3148471.391292882</v>
       </c>
-      <c r="F19" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="39" t="inlineStr">
+      <c r="F19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <f>E19/SQRT(100)</f>
+        <v>314847.1391292882</v>
+      </c>
+      <c r="I19" s="5" t="str">
+        <f>IF(F19=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J19" s="9">
+        <f>D19-SUMIFS($D$5:$D$22,$A$5:$A$22,A19,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="35" t="str">
+        <f>IF(AND(B19=PuntoReorden,C19=CantPedido),"Recomendada","")</f>
+        <v>Recomendada</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Recomendada (cargada en Parametros)</t>
+          <t>¿La recomendada empata con la mejor?</t>
         </is>
+      </c>
+      <c r="R19" s="37" t="str">
+        <f>INDEX($V$5:$V$13,MATCH("s="&amp;PuntoReorden&amp;", Q="&amp;CantPedido,$M$5:$M$13,0))</f>
+        <v>Sí</v>
       </c>
     </row>
     <row r="20">
@@ -57065,7 +57672,22 @@
       <c r="G20" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="9">
+        <f>E20/SQRT(100)</f>
+        <v>387595.8431383146</v>
+      </c>
+      <c r="I20" s="5" t="str">
+        <f>IF(F20=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J20" s="9">
+        <f>D20-SUMIFS($D$5:$D$22,$A$5:$A$22,A20,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>359785.59999999404</v>
+      </c>
+      <c r="K20" s="35" t="str">
+        <f>IF(AND(B20=PuntoReorden,C20=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -57091,7 +57713,22 @@
       <c r="G21" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="9">
+        <f>E21/SQRT(100)</f>
+        <v>551899.6171992046</v>
+      </c>
+      <c r="I21" s="5" t="str">
+        <f>IF(F21=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J21" s="9">
+        <f>D21-SUMIFS($D$5:$D$22,$A$5:$A$22,A21,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-1689222.800000012</v>
+      </c>
+      <c r="K21" s="35" t="str">
+        <f>IF(AND(B21=PuntoReorden,C21=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -57117,7 +57754,22 @@
       <c r="G22" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="7" t="n"/>
+      <c r="H22" s="9">
+        <f>E22/SQRT(100)</f>
+        <v>326508.20965882076</v>
+      </c>
+      <c r="I22" s="5" t="str">
+        <f>IF(F22=0,"Sí","No")</f>
+        <v>Sí</v>
+      </c>
+      <c r="J22" s="9">
+        <f>D22-SUMIFS($D$5:$D$22,$A$5:$A$22,A22,$B$5:$B$22,PuntoReorden,$C$5:$C$22,CantPedido)</f>
+        <v>-270178</v>
+      </c>
+      <c r="K22" s="35" t="str">
+        <f>IF(AND(B22=PuntoReorden,C22=CantPedido),"Recomendada","")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -57143,11 +57795,21 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>3. Riesgo: si las diferencias son menores que el error de Montecarlo, la de menor desviación estándar.</t>
+          <t>3. Riesgo y precisión: si la brecha con la mejor es menor que dos errores estándar, se trata como empate y se decide con la teoría (pregunta 6) y la corrida de 1000 réplicas de la Parte B.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A5:K22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND($B5=PuntoReorden,$C5=CantPedido)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:V13">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND($N5=PuntoReorden,$O5=CantPedido)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
